--- a/artfynd/A 4041-2023 artfynd.xlsx
+++ b/artfynd/A 4041-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4041-2023 artfynd.xlsx
+++ b/artfynd/A 4041-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106779762</v>
+        <v>106780100</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +710,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kunglid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587417.9651345549</v>
+        <v>587468</v>
       </c>
       <c r="R2" t="n">
-        <v>6336906.376761019</v>
+        <v>6336866</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,24 +747,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,49 +765,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106779765</v>
+        <v>106780187</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,17 +812,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kunglid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587422.8567228625</v>
+        <v>587498</v>
       </c>
       <c r="R3" t="n">
-        <v>6336931.971269592</v>
+        <v>6336873</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,24 +849,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,65 +867,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106779772</v>
+        <v>106780197</v>
       </c>
       <c r="B4" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kungslid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587401.9023402596</v>
+        <v>587414</v>
       </c>
       <c r="R4" t="n">
-        <v>6336920.679852724</v>
+        <v>6336922</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,92 +954,79 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106779778</v>
+        <v>106740104</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587368.794118355</v>
+        <v>587530</v>
       </c>
       <c r="R5" t="n">
-        <v>6336944.384055736</v>
+        <v>6336898</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1055,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1065,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,66 +1080,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106779766</v>
+        <v>106779750</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587432.7835268936</v>
+        <v>587402</v>
       </c>
       <c r="R6" t="n">
-        <v>6336925.131157693</v>
+        <v>6336921</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1220,24 +1160,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 exemplar</t>
+          <t>Hack från födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,7 +1176,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,64 +1187,56 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106779757</v>
+        <v>106747201</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587420.8679079768</v>
+        <v>587446</v>
       </c>
       <c r="R7" t="n">
-        <v>6336923.251400336</v>
+        <v>6336914</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1265,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1275,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>13 exemplar</t>
+          <t>Gnag och kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,73 +1289,63 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106779760</v>
+        <v>106779772</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>587455.7698644322</v>
+        <v>587402</v>
       </c>
       <c r="R8" t="n">
-        <v>6336917.483358482</v>
+        <v>6336921</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1464,33 +1375,17 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>6 exemplar</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1502,22 +1397,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106779763</v>
+        <v>106780118</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,41 +1415,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kungslid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>587535.1421167137</v>
+        <v>587453</v>
       </c>
       <c r="R9" t="n">
-        <v>6336890.42281328</v>
+        <v>6336907</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,60 +1484,39 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106779753</v>
+        <v>106780120</v>
       </c>
       <c r="B10" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,37 +1524,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219677</v>
+        <v>103044</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kungslid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587460.6815545561</v>
+        <v>587453</v>
       </c>
       <c r="R10" t="n">
-        <v>6336916.502839863</v>
+        <v>6336907</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,19 +1593,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,69 +1610,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106779758</v>
+        <v>106743482</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>587425.8600547549</v>
+        <v>587423</v>
       </c>
       <c r="R11" t="n">
-        <v>6336918.476049731</v>
+        <v>6336889</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,12 +1703,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>8 exemplar</t>
+          <t>Gnaggång och kläckhål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,34 +1717,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106779777</v>
+        <v>106762954</v>
       </c>
       <c r="B12" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1881,37 +1746,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>587396.0881726602</v>
+        <v>587438</v>
       </c>
       <c r="R12" t="n">
-        <v>6336912.963592918</v>
+        <v>6336994</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1938,19 +1804,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,69 +1821,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106779754</v>
+        <v>106766096</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>587421.0863226126</v>
+        <v>587519</v>
       </c>
       <c r="R13" t="n">
-        <v>6336912.951244394</v>
+        <v>6337003</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2054,99 +1902,74 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>100 exemplar</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106779764</v>
+        <v>106779751</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>587447.1018600496</v>
+        <v>587397</v>
       </c>
       <c r="R14" t="n">
-        <v>6336916.214774436</v>
+        <v>6336946</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2176,33 +1999,17 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 exemplar</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2214,65 +2021,55 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106740092</v>
+        <v>106779752</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>587531.4663875619</v>
+        <v>587427</v>
       </c>
       <c r="R15" t="n">
-        <v>6336884.378788116</v>
+        <v>6336906</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2299,19 +2096,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,73 +2113,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106780092</v>
+        <v>106779753</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587468.3755878494</v>
+        <v>587461</v>
       </c>
       <c r="R16" t="n">
-        <v>6336886.836289869</v>
+        <v>6336917</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2419,77 +2193,61 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106779761</v>
+        <v>106780190</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219677</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2499,17 +2257,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kungslid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>587414.7894003729</v>
+        <v>587499</v>
       </c>
       <c r="R17" t="n">
-        <v>6336928.00371603</v>
+        <v>6336978</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,24 +2294,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,27 +2312,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>106762377</v>
+        <v>106780231</v>
       </c>
       <c r="B18" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,35 +2335,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kungslid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>587498.4079629341</v>
+        <v>587436</v>
       </c>
       <c r="R18" t="n">
-        <v>6336956.895297809</v>
+        <v>6336983</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2655,79 +2396,69 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Amanda Tas</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>106759505</v>
+        <v>106739552</v>
       </c>
       <c r="B19" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2735,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>587481.5232912173</v>
+        <v>587526</v>
       </c>
       <c r="R19" t="n">
-        <v>6336958.706381228</v>
+        <v>6336864</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2770,7 +2501,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,7 +2511,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2807,54 +2538,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>106780213</v>
+        <v>106739951</v>
       </c>
       <c r="B20" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>587388.417688866</v>
+        <v>587525</v>
       </c>
       <c r="R20" t="n">
-        <v>6336941.545852958</v>
+        <v>6336863</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2886,7 +2613,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2896,7 +2623,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,34 +2632,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>106779755</v>
+        <v>106740092</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2957,24 +2678,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>587430.8867035125</v>
+        <v>587531</v>
       </c>
       <c r="R21" t="n">
-        <v>6336912.07435682</v>
+        <v>6336885</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3003,7 +2725,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,12 +2735,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>20 exemplar</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,81 +2744,68 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Tas, Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>106780118</v>
+        <v>106742400</v>
       </c>
       <c r="B22" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>587452.7177325088</v>
+        <v>587424</v>
       </c>
       <c r="R22" t="n">
-        <v>6336907.656166323</v>
+        <v>6336867</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3133,7 +2837,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3143,7 +2847,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,69 +2862,62 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>106780197</v>
+        <v>106746214</v>
       </c>
       <c r="B23" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>587413.8294682073</v>
+        <v>587441</v>
       </c>
       <c r="R23" t="n">
-        <v>6336922.017443069</v>
+        <v>6336903</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3252,7 +2949,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3262,7 +2959,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3271,59 +2968,57 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>106747201</v>
+        <v>106749316</v>
       </c>
       <c r="B24" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3331,10 +3026,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>587446.0499808616</v>
+        <v>587438</v>
       </c>
       <c r="R24" t="n">
-        <v>6336914.565389567</v>
+        <v>6336918</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3366,7 +3061,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3376,12 +3071,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gnag och kläckhål</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,15 +3098,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>106749316</v>
+        <v>106752946</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,7 +3128,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3453,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>587437.8216765724</v>
+        <v>587418</v>
       </c>
       <c r="R25" t="n">
-        <v>6336918.187369985</v>
+        <v>6336899</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3488,7 +3173,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3498,7 +3183,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3525,53 +3210,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>106779779</v>
+        <v>106755705</v>
       </c>
       <c r="B26" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>587379.8876002126</v>
+        <v>587428</v>
       </c>
       <c r="R26" t="n">
-        <v>6336933.772085582</v>
+        <v>6336923</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3600,7 +3281,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3610,7 +3291,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3625,27 +3311,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>106780133</v>
+        <v>106756873</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,23 +3353,20 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>587452.6947331727</v>
+        <v>587449</v>
       </c>
       <c r="R27" t="n">
-        <v>6336908.740395934</v>
+        <v>6336927</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3720,7 +3398,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3730,7 +3408,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3739,34 +3417,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>106756873</v>
+        <v>106779754</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3791,25 +3463,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>587448.5129396369</v>
+        <v>587421</v>
       </c>
       <c r="R28" t="n">
-        <v>6336926.549488263</v>
+        <v>6336913</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3836,19 +3507,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>15:44</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>100 exemplar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3857,33 +3523,29 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>106755705</v>
+        <v>106779755</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,20 +3571,23 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>587429.0157103809</v>
+        <v>587431</v>
       </c>
       <c r="R29" t="n">
-        <v>6336923.424182495</v>
+        <v>6336912</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3949,24 +3614,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>100-tal plantor</t>
+          <t>20 exemplar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3975,68 +3630,68 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>106779773</v>
+        <v>106779756</v>
       </c>
       <c r="B30" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>587496.2697493159</v>
+        <v>587452</v>
       </c>
       <c r="R30" t="n">
-        <v>6336955.222858494</v>
+        <v>6336900</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -4066,19 +3721,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>15 exemplar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,6 +3737,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4098,22 +3749,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>106779769</v>
+        <v>106779757</v>
       </c>
       <c r="B31" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4149,10 +3795,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>587538.7487690713</v>
+        <v>587421</v>
       </c>
       <c r="R31" t="n">
-        <v>6336899.719530585</v>
+        <v>6336923</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -4182,24 +3828,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1 exemplar</t>
+          <t>13 exemplar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4227,54 +3863,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>106740104</v>
+        <v>106779758</v>
       </c>
       <c r="B32" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>587530.0807474731</v>
+        <v>587426</v>
       </c>
       <c r="R32" t="n">
-        <v>6336898.450767088</v>
+        <v>6336918</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4301,19 +3935,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:40</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>8 exemplar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4322,68 +3951,68 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>106779751</v>
+        <v>106779760</v>
       </c>
       <c r="B33" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>587397.5598835748</v>
+        <v>587456</v>
       </c>
       <c r="R33" t="n">
-        <v>6336946.078482135</v>
+        <v>6336918</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4413,19 +4042,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>6 exemplar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4434,6 +4058,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4445,57 +4070,56 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>106779775</v>
+        <v>106779761</v>
       </c>
       <c r="B34" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>587493.530825573</v>
+        <v>587415</v>
       </c>
       <c r="R34" t="n">
-        <v>6336956.249435414</v>
+        <v>6336928</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4525,19 +4149,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4546,6 +4165,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4557,57 +4177,56 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>106779774</v>
+        <v>106779762</v>
       </c>
       <c r="B35" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>587467.4810645088</v>
+        <v>587418</v>
       </c>
       <c r="R35" t="n">
-        <v>6336954.611961979</v>
+        <v>6336906</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4637,19 +4256,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4658,6 +4272,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4669,22 +4284,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>106779756</v>
+        <v>106779763</v>
       </c>
       <c r="B36" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4720,10 +4330,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>587451.780848568</v>
+        <v>587535</v>
       </c>
       <c r="R36" t="n">
-        <v>6336900.585622161</v>
+        <v>6336891</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4753,24 +4363,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>15 exemplar</t>
+          <t>5 exemplar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4798,37 +4398,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>106780205</v>
+        <v>106779764</v>
       </c>
       <c r="B37" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4838,17 +4433,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>587487.2542238093</v>
+        <v>587447</v>
       </c>
       <c r="R37" t="n">
-        <v>6336944.726810342</v>
+        <v>6336916</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4875,19 +4470,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4903,62 +4493,61 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>106779776</v>
+        <v>106779765</v>
       </c>
       <c r="B38" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>587506.2656661103</v>
+        <v>587423</v>
       </c>
       <c r="R38" t="n">
-        <v>6336945.130300806</v>
+        <v>6336932</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4988,19 +4577,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>3 exemplar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5009,6 +4593,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5020,22 +4605,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>106780155</v>
+        <v>106779766</v>
       </c>
       <c r="B39" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5060,28 +4640,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>587393.4557430185</v>
+        <v>587433</v>
       </c>
       <c r="R39" t="n">
-        <v>6336934.602041424</v>
+        <v>6336925</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5108,19 +4684,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5136,12 +4707,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5151,12 +4722,7 @@
         <v>106779767</v>
       </c>
       <c r="B40" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5192,10 +4758,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>587499.4985935277</v>
+        <v>587499</v>
       </c>
       <c r="R40" t="n">
-        <v>6336879.903649217</v>
+        <v>6336880</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -5225,19 +4791,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5270,50 +4826,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>106779752</v>
+        <v>106779768</v>
       </c>
       <c r="B41" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>587427.2108446519</v>
+        <v>587505</v>
       </c>
       <c r="R41" t="n">
-        <v>6336906.030460159</v>
+        <v>6336858</v>
       </c>
       <c r="S41" t="n">
         <v>20</v>
@@ -5343,19 +4898,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 exemplar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,6 +4914,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5375,22 +4926,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>106746214</v>
+        <v>106779769</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5415,25 +4961,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>587440.8480626327</v>
+        <v>587539</v>
       </c>
       <c r="R42" t="n">
-        <v>6336903.607883696</v>
+        <v>6336899</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5460,19 +5005,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:13</t>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1 exemplar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5481,55 +5021,51 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>106780190</v>
+        <v>106779770</v>
       </c>
       <c r="B43" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219677</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5539,17 +5075,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kungslid, Påskallavik, Sm</t>
+          <t>Kungslid, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>587499.0455993356</v>
+        <v>587538</v>
       </c>
       <c r="R43" t="n">
-        <v>6336978.06053159</v>
+        <v>6336875</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5576,19 +5112,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1 exemplar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5604,65 +5135,68 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Brenander, Amanda Tas</t>
+          <t>Amanda Tas, Jan Brenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>106779750</v>
+        <v>106780092</v>
       </c>
       <c r="B44" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kungslid, Sm</t>
+          <t>Kungslid, Påskallavik, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>587401.9023402596</v>
+        <v>587468</v>
       </c>
       <c r="R44" t="n">
-        <v>6336920.679852724</v>
+        <v>6336887</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5689,47 +5223,1450 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack från födosök</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>106780133</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kungslid, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>587453</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6336908</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>106780155</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kungslid, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>587394</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6336935</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>106780162</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kungslid, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>587524</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6336856</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>106759505</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>587481</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6336959</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>106760419</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>587498</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6336957</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>106779773</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>587497</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6336955</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
           <t>Amanda Tas</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
+      <c r="AX50" t="inlineStr">
         <is>
           <t>Amanda Tas</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>106779774</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>587467</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6336955</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>106779775</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>587493</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6336956</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>106779776</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>587507</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6336945</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>106779777</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>587396</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6336913</v>
+      </c>
+      <c r="S54" t="n">
+        <v>20</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>106779778</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>587369</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6336945</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>106779779</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kungslid, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>587380</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6336933</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>106780205</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kungslid, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>587488</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6336945</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>106780213</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kungslid, Påskallavik, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>587389</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6336942</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Döderhult</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-02-14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4041-2023 artfynd.xlsx
+++ b/artfynd/A 4041-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780187</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780197</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106740104</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779750</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106747201</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779772</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780118</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1619,6 +1664,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780120</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106743482</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106762954</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106766096</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2025,6 +2090,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779751</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779752</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779753</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780190</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780231</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2535,6 +2625,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106739552</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2647,6 +2742,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106739951</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,6 +2859,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106740092</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2871,6 +2976,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106742400</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2983,6 +3093,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106746214</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3095,6 +3210,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106749316</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106752946</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3320,6 +3445,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106755705</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106756873</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3539,6 +3674,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779754</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3646,6 +3786,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779755</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3753,6 +3898,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779756</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3860,6 +4010,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779757</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3967,6 +4122,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779758</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4074,6 +4234,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779760</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4181,6 +4346,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779761</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4288,6 +4458,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779762</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4395,6 +4570,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779763</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4502,6 +4682,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779764</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4609,6 +4794,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779765</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4716,6 +4906,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779766</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4823,6 +5018,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779767</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4930,6 +5130,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779768</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5037,6 +5242,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779769</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5144,6 +5354,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779770</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5250,6 +5465,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780092</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5356,6 +5576,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780133</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5462,6 +5687,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780155</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5568,6 +5798,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780162</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5676,6 +5911,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106759505</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5784,6 +6024,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106760419</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5881,6 +6126,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779773</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5978,6 +6228,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779774</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6075,6 +6330,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779775</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6172,6 +6432,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779776</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6269,6 +6534,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779777</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6366,6 +6636,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779778</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6463,6 +6738,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779779</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6565,6 +6845,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780205</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6667,8 +6952,72 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106780213</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>